--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +38,24 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00B00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -50,8 +67,28 @@
         <fgColor rgb="0016335E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A4FD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0015A06A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9822B"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -73,11 +110,25 @@
         <color rgb="00D0D7E2"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E6EAF0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E6EAF0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E6EAF0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E6EAF0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,6 +145,22 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1326,4 +1393,744 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>⚠ 자동 생성 탭 — 직접 편집하지 마세요. 일정은 '업무리스트' 탭에서 수정 후 python sync_excel.py 실행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>업무명</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>'26 1월</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>4월</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>5월</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>9월</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>10월</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>11월</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>12월</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>'27 1월</t>
+        </is>
+      </c>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>사업 운영·관리</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>2차년도 협약 체결·연구비 카드 등록·집행계획 수립</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-02~2026-03-12</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="12" t="n"/>
+      <c r="L3" s="12" t="n"/>
+      <c r="M3" s="12" t="n"/>
+      <c r="N3" s="12" t="n"/>
+      <c r="O3" s="12" t="n"/>
+      <c r="P3" s="12" t="n"/>
+      <c r="Q3" s="12" t="n"/>
+      <c r="R3" s="12" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr"/>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>참여연구원 등록·변경 및 인건비 계상 관리</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-05~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="11" t="n"/>
+      <c r="L4" s="11" t="n"/>
+      <c r="M4" s="11" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="11" t="n"/>
+      <c r="P4" s="12" t="n"/>
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="12" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>운영위원회 개최 (연 1회 이상)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-01~2026-09-30</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="12" t="n"/>
+      <c r="Q5" s="12" t="n"/>
+      <c r="R5" s="12" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr"/>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>세부과제(1~5) 진척도 정기 점검 회의</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="11" t="n"/>
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr"/>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>KPI 기반 진척도 모니터링·조기경보(Early Warning)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-05~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
+      <c r="N7" s="11" t="n"/>
+      <c r="O7" s="11" t="n"/>
+      <c r="P7" s="12" t="n"/>
+      <c r="Q7" s="12" t="n"/>
+      <c r="R7" s="12" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr"/>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>외부 전문가 Peer-review (내부 모니터링 병행)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-01~2026-11-30</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="11" t="n"/>
+      <c r="O8" s="12" t="n"/>
+      <c r="P8" s="12" t="n"/>
+      <c r="Q8" s="12" t="n"/>
+      <c r="R8" s="12" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>부진과제 컨설팅·개선계획 수립 (필요시)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-01~2026-12-15</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11" t="n"/>
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="12" t="n"/>
+      <c r="R9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>연구노트·보안등급·연구윤리 관리</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-05~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="11" t="n"/>
+      <c r="N10" s="11" t="n"/>
+      <c r="O10" s="11" t="n"/>
+      <c r="P10" s="12" t="n"/>
+      <c r="Q10" s="12" t="n"/>
+      <c r="R10" s="12" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>국제협력 (KIMM–DLR)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>KIMM–DLR 협력채널 유지·실무 협의</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-05~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="13" t="n"/>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="13" t="n"/>
+      <c r="P11" s="12" t="n"/>
+      <c r="Q11" s="12" t="n"/>
+      <c r="R11" s="12" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr"/>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>국제 워크숍 — 한국(기계연) 준비·개최</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-16~2026-08-05</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
+      <c r="P12" s="12" t="n"/>
+      <c r="Q12" s="12" t="n"/>
+      <c r="R12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>국제 워크숍/기술교류 — 독일(DLR) 방문</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-01~2026-11-15</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="12" t="n"/>
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="12" t="n"/>
+      <c r="R13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr"/>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>연구인력 교류 — DLR 파견·방문연구·세미나 지원</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="13" t="n"/>
+      <c r="P14" s="12" t="n"/>
+      <c r="Q14" s="12" t="n"/>
+      <c r="R14" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>EKC 한-유럽 과학기술학술회의 특별세션 개설·발표</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-01~2026-07-31</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="12" t="n"/>
+      <c r="P15" s="12" t="n"/>
+      <c r="Q15" s="12" t="n"/>
+      <c r="R15" s="12" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>성과 관리</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>공동 논문(공동저자)·특허(공동출원) 성과 관리</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="12" t="n"/>
+      <c r="Q16" s="12" t="n"/>
+      <c r="R16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>DLR 공동특허 출원·기술이전 체계 운영</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="12" t="n"/>
+      <c r="R17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>수요기업 사업화 설명회 (단계별 1회)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-01~2026-10-31</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="12" t="n"/>
+      <c r="P18" s="12" t="n"/>
+      <c r="Q18" s="12" t="n"/>
+      <c r="R18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>성과집·기술 브로슈어 발간</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="12" t="n"/>
+      <c r="Q19" s="12" t="n"/>
+      <c r="R19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>평가·보고 (연차 마감)</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>2차년도 연차실적보고서 작성·제출</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-01~2027-02-15</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
+      <c r="R20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>2차년도 연구비 집행 점검·정산</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-02~2027-02-28</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
+      <c r="P21" s="15" t="n"/>
+      <c r="Q21" s="15" t="n"/>
+      <c r="R21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>자체평가·연차평가(점검) 대응</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-15~2027-01-31</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="12" t="n"/>
+      <c r="R22" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>3차년도 사업계획서·협약 준비</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-01~2027-03-15</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="15" t="n"/>
+      <c r="Q23" s="15" t="n"/>
+      <c r="R23" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성능목표실적" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정량성과" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -248,14 +250,39 @@
         <t>같은 키끼리 한 카테고리로 묶임. 막대 색은 키 등장 순서대로 자동(파랑·보라·초록·주황).</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>계획 시작/종료 — 간트 위쪽(계획) 바.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>실적 시작/종료 — 간트 아래쪽(실적) 바. 비우면 실적 바 없음.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>계획서 또는 행정 (비우면 배지 없음).</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>총괄/운영위/DLR/전담 중 쉼표로 구분. 세부과제는 보통 비움.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>sync_excel</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>예: 85% (수동 입력).</t>
       </text>
     </comment>
   </commentList>
@@ -551,17 +578,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,25 +611,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>시작일</t>
+          <t>계획시작</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>종료일</t>
+          <t>계획종료</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>실적시작</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>실적종료</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>주관</t>
         </is>
@@ -628,17 +667,23 @@
       <c r="E2" s="5" t="n">
         <v>46093</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>협약 3/12 기준</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="5" t="n">
+        <v>46027</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>46101</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>협약 3/12 기준 (실적 예시)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>행정</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -666,17 +711,19 @@
       <c r="E3" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>연중 상시</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>행정</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -704,17 +751,19 @@
       <c r="E4" s="5" t="n">
         <v>46295</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>KETEP 간사·국내전문가(가스터빈·수전해) 포함</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>운영위</t>
         </is>
@@ -742,17 +791,19 @@
       <c r="E5" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>분기별 (3·6·9·12월)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -780,17 +831,19 @@
       <c r="E6" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>연차·분기 보고 체계</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -818,13 +871,15 @@
       <c r="E7" s="5" t="n">
         <v>46356</v>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -852,17 +907,19 @@
       <c r="E8" s="5" t="n">
         <v>46371</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>조건부 수행</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -890,17 +947,19 @@
       <c r="E9" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>보안등급 분류 기준</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -928,17 +987,19 @@
       <c r="E10" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>내부협의체 정기 운영</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>총괄, DLR</t>
         </is>
@@ -966,17 +1027,19 @@
       <c r="E11" s="5" t="n">
         <v>46239</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>8/5 개최 (워크숍 탭 참조)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -1004,17 +1067,19 @@
       <c r="E12" s="5" t="n">
         <v>46341</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>한·독 각 1회 이상</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>총괄, DLR</t>
         </is>
@@ -1042,17 +1107,19 @@
       <c r="E13" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>하반기 집중</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>총괄, DLR</t>
         </is>
@@ -1080,17 +1147,19 @@
       <c r="E14" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>에너지/기계 분과 세션</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -1118,17 +1187,19 @@
       <c r="E15" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>공동소유·활용 계약 기반</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>총괄, DLR</t>
         </is>
@@ -1156,13 +1227,15 @@
       <c r="E16" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>총괄, DLR</t>
         </is>
@@ -1190,17 +1263,19 @@
       <c r="E17" s="5" t="n">
         <v>46326</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>국내 수요기업 대상</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -1228,13 +1303,15 @@
       <c r="E18" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>계획서</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -1262,17 +1339,19 @@
       <c r="E19" s="5" t="n">
         <v>46433</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>KETEP 제출</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>행정</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -1300,13 +1379,15 @@
       <c r="E20" s="5" t="n">
         <v>46446</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>행정</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -1334,13 +1415,15 @@
       <c r="E21" s="5" t="n">
         <v>46418</v>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>행정</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -1368,17 +1451,19 @@
       <c r="E22" s="5" t="n">
         <v>46461</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>차년도 연속 수행</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>행정</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>총괄</t>
         </is>
@@ -1386,7 +1471,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"계획서,행정"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1396,6 +1481,242 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>평가항목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>목표</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>실적</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>달성도</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>(예시) 평가항목 1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>(목표값)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(실적값)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>예시 — 실제 내용으로 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>(예시) 평가항목 2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>성과구분</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>목표</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>실적</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SCI(E) 논문</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>편</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>특허 출원(국내·국제)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>건</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>학술회의 발표</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>건</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1427,7 +1748,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>⚠ 자동 생성 탭 — 직접 편집하지 마세요. 일정은 '업무리스트' 탭에서 수정 후 python sync_excel.py 실행.</t>
+          <t>⚠ 자동 생성 탭(계획 기준 미리보기) — 직접 편집 금지. 일정은 '업무리스트'에서 수정 후 python sync_excel.py.</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1765,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>기간</t>
+          <t>계획기간</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -648,826 +648,282 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>사업 운영·관리</t>
+          <t>운영·관리</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2차년도 협약 체결·연구비 카드 등록·집행계획 수립</t>
+          <t>2차년도 협약 체결 및 연구추진체계 정비</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>46093</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>46027</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>46101</v>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>협약 3/12 기준 (실적 예시)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>행정</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
+        <v>46081</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>사업 운영·관리</t>
+          <t>운영·관리</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>참여연구원 등록·변경 및 인건비 계상 관리</t>
+          <t>수소 생산 및 무탄소 발전 핵심 부품 설계·단위기술 성능 확보 추진점검</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>46387</v>
       </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>연중 상시</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>행정</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>사업 운영·관리</t>
+          <t>운영·관리</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>운영위원회 개최 (연 1회 이상)</t>
+          <t>세부과제 연계 강화 및 분기별 진도 점검</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>46266</v>
+        <v>46082</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>KETEP 간사·국내전문가(가스터빈·수전해) 포함</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>운영위</t>
-        </is>
-      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>사업 운영·관리</t>
+          <t>운영·관리</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>세부과제(1~5) 진척도 정기 점검 회의</t>
+          <t>운영위원회 개최(국외 1회·국내 1회)</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>분기별 (3·6·9·12월)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>사업 운영·관리</t>
+          <t>국제협력</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>KPI 기반 진척도 모니터링·조기경보(Early Warning)</t>
+          <t>국제협력 공동연구 본격화 및 DLR 협력 일정 조율</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>46027</v>
+        <v>46054</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>46387</v>
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>연차·분기 보고 체계</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>사업 운영·관리</t>
+          <t>국제협력</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>외부 전문가 Peer-review (내부 모니터링 병행)</t>
+          <t>국제워크숍 개최</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>46356</v>
+        <v>46326</v>
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>사업 운영·관리</t>
+          <t>국제협력</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>부진과제 컨설팅·개선계획 수립 (필요시)</t>
+          <t>DLR 방문 및 해외 참여기관 인력교류 추진</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>46327</v>
+        <v>46082</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>46371</v>
+        <v>46387</v>
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>조건부 수행</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>사업 운영·관리</t>
+          <t>성과관리</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>연구노트·보안등급·연구윤리 관리</t>
+          <t>수요기업 사업화설명회 개최</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>46027</v>
+        <v>46174</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>보안등급 분류 기준</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>국제협력 (KIMM–DLR)</t>
+          <t>성과관리</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>KIMM–DLR 협력채널 유지·실무 협의</t>
+          <t>성과지표(논문·특허·기술교류) 관리 및 취합</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>46387</v>
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>내부협의체 정기 운영</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>총괄, DLR</t>
-        </is>
-      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>국제협력 (KIMM–DLR)</t>
+          <t>평가·보고</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>국제 워크숍 — 한국(기계연) 준비·개최</t>
+          <t>2차년도 연차실적 평가 및 연차보고서 작성·제출</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>46189</v>
+        <v>46296</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>46239</v>
+        <v>46387</v>
       </c>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>8/5 개최 (워크숍 탭 참조)</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>국제협력 (KIMM–DLR)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>국제 워크숍/기술교류 — 독일(DLR) 방문</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>46341</v>
-      </c>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>한·독 각 1회 이상</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>총괄, DLR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>국제협력 (KIMM–DLR)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>연구인력 교류 — DLR 파견·방문연구·세미나 지원</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>하반기 집중</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>총괄, DLR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>국제협력 (KIMM–DLR)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>EKC 한-유럽 과학기술학술회의 특별세션 개설·발표</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>46143</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>에너지/기계 분과 세션</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>성과 관리</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>공동 논문(공동저자)·특허(공동출원) 성과 관리</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>46082</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>공동소유·활용 계약 기반</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>총괄, DLR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>성과 관리</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>DLR 공동특허 출원·기술이전 체계 운영</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>총괄, DLR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>성과 관리</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>수요기업 사업화 설명회 (단계별 1회)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>46326</v>
-      </c>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>국내 수요기업 대상</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>성과 관리</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>성과집·기술 브로슈어 발간</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>46327</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>계획서</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>평가·보고 (연차 마감)</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2차년도 연차실적보고서 작성·제출</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>46357</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>46433</v>
-      </c>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>KETEP 제출</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>행정</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>평가·보고 (연차 마감)</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2차년도 연구비 집행 점검·정산</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>46389</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>46446</v>
-      </c>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>행정</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>평가·보고 (연차 마감)</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>자체평가·연차평가(점검) 대응</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>46371</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>46418</v>
-      </c>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>행정</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>평가·보고 (연차 마감)</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>3차년도 사업계획서·협약 준비</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>46327</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>46461</v>
-      </c>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>차년도 연속 수행</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>행정</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1486,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1532,52 +988,92 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>(예시) 평가항목 1</t>
+          <t>운영위원회 개최</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>회</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>(목표값)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>(실적값)</t>
-        </is>
-      </c>
+          <t>2(국외1, 국내1)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>예시 — 실제 내용으로 교체</t>
+          <t>1차년도 실적 1회</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>(예시) 평가항목 2</t>
+          <t>국제워크숍 개최</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>회</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>예시</t>
+          <t>1차년도 실적 1회</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>수요기업 사업화설명회</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>세부과제 진도 점검</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4(분기별)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>관리 KPI(보고서 명시 수치 아님, 분기 점검 가정)</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1129,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SCI(E) 논문</t>
+          <t>국제워크숍</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>편</t>
+          <t>회</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1648,68 +1144,60 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>예시</t>
+          <t>1차년도 실적 1회</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>특허 출원(국내·국제)</t>
+          <t>운영위원회</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>건</t>
+          <t>회</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>2(국외1, 국내1)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>예시</t>
+          <t>1차년도 실적 1회(국외1)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>학술회의 발표</t>
+          <t>수요기업 사업화설명회</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>건</t>
+          <t>회</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>예시</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1722,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1847,22 +1335,22 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>사업 운영·관리</t>
+          <t>운영·관리</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>2차년도 협약 체결·연구비 카드 등록·집행계획 수립</t>
+          <t>2차년도 협약 체결 및 연구추진체계 정비</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>2026-01-02~2026-03-12</t>
+          <t>2026-01-01~2026-02-28</t>
         </is>
       </c>
       <c r="D3" s="11" t="n"/>
       <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
+      <c r="F3" s="12" t="n"/>
       <c r="G3" s="12" t="n"/>
       <c r="H3" s="12" t="n"/>
       <c r="I3" s="12" t="n"/>
@@ -1880,12 +1368,12 @@
       <c r="A4" s="8" t="inlineStr"/>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>참여연구원 등록·변경 및 인건비 계상 관리</t>
+          <t>수소 생산 및 무탄소 발전 핵심 부품 설계·단위기술 성능 확보 추진점검</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>2026-01-05~2026-12-31</t>
+          <t>2026-01-01~2026-12-31</t>
         </is>
       </c>
       <c r="D4" s="11" t="n"/>
@@ -1908,26 +1396,26 @@
       <c r="A5" s="8" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>운영위원회 개최 (연 1회 이상)</t>
+          <t>세부과제 연계 강화 및 분기별 진도 점검</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>2026-09-01~2026-09-30</t>
+          <t>2026-03-01~2026-12-31</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="11" t="n"/>
       <c r="L5" s="11" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="12" t="n"/>
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="11" t="n"/>
       <c r="P5" s="12" t="n"/>
       <c r="Q5" s="12" t="n"/>
       <c r="R5" s="12" t="n"/>
@@ -1936,17 +1424,17 @@
       <c r="A6" s="8" t="inlineStr"/>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>세부과제(1~5) 진척도 정기 점검 회의</t>
+          <t>운영위원회 개최(국외 1회·국내 1회)</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>2026-03-01~2026-12-31</t>
+          <t>2026-04-01~2026-11-30</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="12" t="n"/>
-      <c r="F6" s="11" t="n"/>
+      <c r="F6" s="12" t="n"/>
       <c r="G6" s="11" t="n"/>
       <c r="H6" s="11" t="n"/>
       <c r="I6" s="11" t="n"/>
@@ -1955,35 +1443,39 @@
       <c r="L6" s="11" t="n"/>
       <c r="M6" s="11" t="n"/>
       <c r="N6" s="11" t="n"/>
-      <c r="O6" s="11" t="n"/>
+      <c r="O6" s="12" t="n"/>
       <c r="P6" s="12" t="n"/>
       <c r="Q6" s="12" t="n"/>
       <c r="R6" s="12" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr"/>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>국제협력</t>
+        </is>
+      </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>KPI 기반 진척도 모니터링·조기경보(Early Warning)</t>
+          <t>국제협력 공동연구 본격화 및 DLR 협력 일정 조율</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>2026-01-05~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="n"/>
+          <t>2026-02-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="13" t="n"/>
       <c r="P7" s="12" t="n"/>
       <c r="Q7" s="12" t="n"/>
       <c r="R7" s="12" t="n"/>
@@ -1992,12 +1484,12 @@
       <c r="A8" s="8" t="inlineStr"/>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>외부 전문가 Peer-review (내부 모니터링 병행)</t>
+          <t>국제워크숍 개최</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-01~2026-11-30</t>
+          <t>2026-09-01~2026-10-31</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -2008,9 +1500,9 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
       <c r="P8" s="12" t="n"/>
       <c r="Q8" s="12" t="n"/>
@@ -2020,100 +1512,104 @@
       <c r="A9" s="8" t="inlineStr"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>부진과제 컨설팅·개선계획 수립 (필요시)</t>
+          <t>DLR 방문 및 해외 참여기관 인력교류 추진</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>2026-11-01~2026-12-15</t>
+          <t>2026-03-01~2026-12-31</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
       <c r="P9" s="12" t="n"/>
       <c r="Q9" s="12" t="n"/>
       <c r="R9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>성과관리</t>
+        </is>
+      </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>연구노트·보안등급·연구윤리 관리</t>
+          <t>수요기업 사업화설명회 개최</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>2026-01-05~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="11" t="n"/>
+          <t>2026-06-01~2026-09-30</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
       <c r="P10" s="12" t="n"/>
       <c r="Q10" s="12" t="n"/>
       <c r="R10" s="12" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>국제협력 (KIMM–DLR)</t>
-        </is>
-      </c>
+      <c r="A11" s="8" t="inlineStr"/>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>KIMM–DLR 협력채널 유지·실무 협의</t>
+          <t>성과지표(논문·특허·기술교류) 관리 및 취합</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>2026-01-05~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="13" t="n"/>
-      <c r="N11" s="13" t="n"/>
-      <c r="O11" s="13" t="n"/>
+          <t>2026-01-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="14" t="n"/>
       <c r="P11" s="12" t="n"/>
       <c r="Q11" s="12" t="n"/>
       <c r="R11" s="12" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>평가·보고</t>
+        </is>
+      </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>국제 워크숍 — 한국(기계연) 준비·개최</t>
+          <t>2차년도 연차실적 평가 및 연차보고서 작성·제출</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>2026-06-16~2026-08-05</t>
+          <t>2026-10-01~2026-12-31</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -2121,332 +1617,16 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="13" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
+      <c r="M12" s="15" t="n"/>
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="15" t="n"/>
       <c r="P12" s="12" t="n"/>
       <c r="Q12" s="12" t="n"/>
       <c r="R12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr"/>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>국제 워크숍/기술교류 — 독일(DLR) 방문</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-01~2026-11-15</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="13" t="n"/>
-      <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="12" t="n"/>
-      <c r="R13" s="12" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr"/>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>연구인력 교류 — DLR 파견·방문연구·세미나 지원</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-01~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="13" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="13" t="n"/>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="12" t="n"/>
-      <c r="R14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr"/>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>EKC 한-유럽 과학기술학술회의 특별세션 개설·발표</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-01~2026-07-31</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="12" t="n"/>
-      <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="12" t="n"/>
-      <c r="R15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>성과 관리</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>공동 논문(공동저자)·특허(공동출원) 성과 관리</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-01~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="12" t="n"/>
-      <c r="R16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr"/>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>DLR 공동특허 출원·기술이전 체계 운영</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-01~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="14" t="n"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="14" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="12" t="n"/>
-      <c r="R17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr"/>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>수요기업 사업화 설명회 (단계별 1회)</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-01~2026-10-31</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="12" t="n"/>
-      <c r="R18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr"/>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>성과집·기술 브로슈어 발간</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-01~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="14" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="12" t="n"/>
-      <c r="R19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>평가·보고 (연차 마감)</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>2차년도 연차실적보고서 작성·제출</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>2026-12-01~2027-02-15</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="12" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="15" t="n"/>
-      <c r="R20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr"/>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>2차년도 연구비 집행 점검·정산</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>2027-01-02~2027-02-28</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="12" t="n"/>
-      <c r="P21" s="15" t="n"/>
-      <c r="Q21" s="15" t="n"/>
-      <c r="R21" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr"/>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>자체평가·연차평가(점검) 대응</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>2026-12-15~2027-01-31</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="12" t="n"/>
-      <c r="R22" s="12" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr"/>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>3차년도 사업계획서·협약 준비</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-01~2027-03-15</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="15" t="n"/>
-      <c r="O23" s="15" t="n"/>
-      <c r="P23" s="15" t="n"/>
-      <c r="Q23" s="15" t="n"/>
-      <c r="R23" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성능목표실적" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정량성과" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정량성과" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -268,21 +267,6 @@
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>총괄/운영위/DLR/전담 중 쉼표로 구분. 세부과제는 보통 비움.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>sync_excel</author>
-  </authors>
-  <commentList>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>예: 85% (수동 입력).</t>
       </text>
     </comment>
   </commentList>
@@ -942,153 +926,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>평가항목</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>목표</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>실적</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>달성도</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>운영위원회 개최</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>회</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2(국외1, 국내1)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1차년도 실적 1회</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>국제워크숍 개최</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>회</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1차년도 실적 1회</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>수요기업 사업화설명회</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>회</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>세부과제 진도 점검</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>회</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4(분기별)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>관리 KPI(보고서 명시 수치 아님, 분기 점검 가정)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1204,7 +1041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정량성과" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주요일정" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -267,6 +268,21 @@
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>총괄/운영위/DLR/전담 중 쉼표로 구분. 세부과제는 보통 비움.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>sync_excel</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>YYYY-MM-DD. 간트차트 위에 ★ 마커로 표시됨.</t>
       </text>
     </comment>
   </commentList>
@@ -1047,6 +1063,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>일정명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>EKC 한-유럽 특별세션</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>에너지/기계 분과</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>국제공동워크숍(KIMM 개최)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>DLR 참석</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>운영위원회</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>연 1회 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>수요기업 사업화 설명회</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>국내 수요기업</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DLR 기술교류·방문(독일)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>46336</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>한·독 교류</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2차년도 연차실적보고서 제출</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>46433</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>KETEP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정량성과" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주요일정" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연구비" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -130,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -163,6 +164,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -283,6 +287,21 @@
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>YYYY-MM-DD. 간트차트 위에 ★ 마커로 표시됨.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>budget</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>단위: 천원</t>
       </text>
     </comment>
   </commentList>
@@ -1190,6 +1209,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>과제</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>정부지원금</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>기관부담</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>총괄</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="C2" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1세부</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="n">
+        <v>2745000</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>323520</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>3068520</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2세부</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>66706</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>2821706</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>3세부</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>295806</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>3045806</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정량성과" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주요일정" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연구비" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연구비" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주요일정" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -281,12 +281,12 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>sync_excel</author>
+    <author>budget</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>YYYY-MM-DD. 간트차트 위에 ★ 마커로 표시됨.</t>
+        <t>단위: 천원</t>
       </text>
     </comment>
   </commentList>
@@ -296,12 +296,12 @@
 <file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>budget</author>
+    <author>sync_excel</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>단위: 천원</t>
+        <t>관련 업무 구분명(예: 국제협력) — 그 카테고리 바 위에 ★ 표시</t>
       </text>
     </comment>
   </commentList>
@@ -1082,120 +1082,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>일정명</t>
+          <t>과제</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>날짜</t>
+          <t>정부지원금</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>기관부담</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>EKC 한-유럽 특별세션</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>46218</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>에너지/기계 분과</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>총괄</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="C2" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>국제공동워크숍(KIMM 개최)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>46239</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>DLR 참석</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1세부</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="n">
+        <v>2745000</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>323520</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>3068520</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>운영위원회</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>46280</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>연 1회 이상</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2세부</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>66706</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>2821706</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>수요기업 사업화 설명회</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>46315</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>국내 수요기업</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>DLR 기술교류·방문(독일)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>46336</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>한·독 교류</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2차년도 연차실적보고서 제출</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>KETEP</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>3세부</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>295806</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>3045806</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1209,110 +1199,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>과제</t>
+          <t>일정명</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>정부지원금</t>
+          <t>날짜</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>기관부담</t>
+          <t>관련구분</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>총괄</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="C2" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="16" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>EKC 한-유럽 특별세션</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>국제협력</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>에너지/기계 분과</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1세부</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n">
-        <v>2745000</v>
-      </c>
-      <c r="C3" s="16" t="n">
-        <v>323520</v>
-      </c>
-      <c r="D3" s="16" t="n">
-        <v>3068520</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>국제공동워크숍(KIMM 개최)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>국제협력</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>DLR 참석</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2세부</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="n">
-        <v>2755000</v>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>66706</v>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>2821706</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>운영위원회</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>운영·관리</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>연 1회 이상</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>3세부</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="n">
-        <v>2750000</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>295806</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>3045806</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>수요기업 사업화 설명회</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>성과관리</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>국내 수요기업</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DLR 기술교류·방문(독일)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>46336</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>국제협력</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>한·독 교류</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2차년도 연차실적보고서 제출</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>46433</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>평가·보고</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>KETEP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -686,8 +686,12 @@
       <c r="E2" s="5" t="n">
         <v>46081</v>
       </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="F2" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>46081</v>
+      </c>
       <c r="H2" s="4" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
@@ -714,8 +718,12 @@
       <c r="E3" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="F3" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>46387</v>
+      </c>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -742,8 +750,12 @@
       <c r="E4" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="F4" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>46387</v>
+      </c>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
@@ -770,8 +782,12 @@
       <c r="E5" s="5" t="n">
         <v>46356</v>
       </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="F5" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>46356</v>
+      </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -798,8 +814,12 @@
       <c r="E6" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="F6" s="5" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>46387</v>
+      </c>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
@@ -826,8 +846,12 @@
       <c r="E7" s="5" t="n">
         <v>46326</v>
       </c>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="F7" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>46326</v>
+      </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
@@ -854,8 +878,12 @@
       <c r="E8" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
+      <c r="F8" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>46387</v>
+      </c>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
@@ -882,8 +910,12 @@
       <c r="E9" s="5" t="n">
         <v>46295</v>
       </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
+      <c r="F9" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>46295</v>
+      </c>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
@@ -910,8 +942,12 @@
       <c r="E10" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="F10" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>46387</v>
+      </c>
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
@@ -938,8 +974,12 @@
       <c r="E11" s="5" t="n">
         <v>46387</v>
       </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="F11" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>46387</v>
+      </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1273,11 +1273,11 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>EKC 한-유럽 특별세션</t>
+          <t>국제공동워크숍(KIMM 개최)</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -1286,27 +1286,27 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>에너지/기계 분과</t>
+          <t>DLR 참석</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>국제공동워크숍(KIMM 개최)</t>
+          <t>수요기업 사업화 설명회</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>46239</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>국제협력</t>
+          <t>성과관리</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>DLR 참석</t>
+          <t>가스터빈 심포지움 2026 (8.26~28)</t>
         </is>
       </c>
     </row>
@@ -1333,58 +1333,18 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>수요기업 사업화 설명회</t>
+          <t>2차년도 연차실적보고서 제출</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46315</v>
+        <v>46433</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>성과관리</t>
+          <t>평가·보고</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>국내 수요기업</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>DLR 기술교류·방문(독일)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>46336</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>국제협력</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>한·독 교류</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2차년도 연차실적보고서 제출</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>평가·보고</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>KETEP</t>
         </is>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무리스트" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="13">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -34,11 +34,56 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FFB00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
     <font>
@@ -53,17 +98,38 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16335E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7A4FD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF15A06A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9822B"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -91,7 +157,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -101,17 +167,33 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7E2"/>
+        <color rgb="FFD0D7E2"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7E2"/>
+        <color rgb="FFD0D7E2"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7E2"/>
+        <color rgb="FFD0D7E2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7E2"/>
+        <color rgb="FFD0D7E2"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE6EAF0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE6EAF0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE6EAF0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE6EAF0"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -131,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -148,7 +230,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -167,9 +248,42 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -597,19 +711,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" style="17" min="1" max="1"/>
+    <col width="18" customWidth="1" style="17" min="2" max="2"/>
+    <col width="46" customWidth="1" style="17" min="3" max="3"/>
+    <col width="12" customWidth="1" style="17" min="4" max="7"/>
+    <col width="24" customWidth="1" style="17" min="8" max="8"/>
+    <col width="9" customWidth="1" style="17" min="9" max="9"/>
+    <col width="14" customWidth="1" style="17" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -675,26 +786,26 @@
           <t>운영·관리</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>2차년도 협약 체결 및 연구추진체계 정비</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>46023</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>46081</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>46081</v>
-      </c>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4세부 과제 연구 기획 및 선정 평가 </t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E2" s="21" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F2" s="21" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>46202</v>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -709,284 +820,208 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>수소 생산 및 무탄소 발전 핵심 부품 설계·단위기술 성능 확보 추진점검</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>46023</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>운영위원회 개최(국외 1회·국내 1회)</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E3" s="21" t="n">
+        <v>46356</v>
+      </c>
+      <c r="F3" s="21" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G3" s="21" t="n">
+        <v>46356</v>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>8월 5일 실시</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>운영·관리</t>
+          <t>국제협력</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>세부과제 연계 강화 및 분기별 진도 점검</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
+          <t>국제워크숍 개최</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E4" s="22" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F4" s="22" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G4" s="22" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>8월 5일</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="32" customHeight="1" s="17">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>국제협력</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>DLR 해외 인력 파견</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="n">
         <v>46082</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E5" s="21" t="n">
         <v>46387</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F5" s="21" t="n">
         <v>46082</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G5" s="21" t="n">
         <v>46387</v>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>운영·관리</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>운영위원회 개최(국외 1회·국내 1회)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>46356</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>46356</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>이원준(2월 중순~5월 중순), 박진영(5월), 황정재(7~8월)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="28.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>국제협력</t>
+          <t>성과관리</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>국제협력 공동연구 본격화 및 DLR 협력 일정 조율</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>46054</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>46054</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>수요기업 사업화설명회 개최</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>가스터빈 심포지움 2026 (8.26~28)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>국제협력</t>
+          <t>성과관리</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>국제워크숍 개최</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>46326</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>46266</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>46326</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>성과지표(논문·특허·기술교류) 관리 및 취합</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>46023</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>46387</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>46023</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>8월 말, 11월 점검 실시</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>국제협력</t>
+          <t>평가·보고</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>DLR 방문 및 해외 참여기관 인력교류 추진</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>46082</v>
-      </c>
-      <c r="E8" s="5" t="n">
+          <t>2차년도 연차실적 평가 및 연차보고서 작성·제출</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E8" s="21" t="n">
         <v>46387</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>46082</v>
-      </c>
-      <c r="G8" s="5" t="n">
+      <c r="F8" s="21" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G8" s="21" t="n">
         <v>46387</v>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>성과관리</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>수요기업 사업화설명회 개최</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>46174</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>46295</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>성과관리</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>성과지표(논문·특허·기술교류) 관리 및 취합</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>46023</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>평가·보고</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>2차년도 연차실적 평가 및 연차보고서 작성·제출</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>46296</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>46387</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="3" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I197" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"계획서,행정"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1002,13 +1037,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" style="17" min="1" max="1"/>
+    <col width="8" customWidth="1" style="17" min="2" max="2"/>
+    <col width="12" customWidth="1" style="17" min="3" max="4"/>
+    <col width="28" customWidth="1" style="17" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,8 +1142,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1123,13 +1157,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" style="17" min="1" max="1"/>
+    <col width="14" customWidth="1" style="17" min="2" max="2"/>
+    <col width="12" customWidth="1" style="17" min="3" max="3"/>
+    <col width="14" customWidth="1" style="17" min="4" max="4"/>
+    <col width="20" customWidth="1" style="17" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,16 +1199,16 @@
           <t>총괄</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="15" t="n">
         <v>1100000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="15" t="n">
         <v>1100000</v>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1182,16 +1216,16 @@
           <t>1세부</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="15" t="n">
         <v>2745000</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="15" t="n">
         <v>323520</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="15" t="n">
         <v>3068520</v>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1199,16 +1233,16 @@
           <t>2세부</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="15" t="n">
         <v>2755000</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="15" t="n">
         <v>66706</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="15" t="n">
         <v>2821706</v>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1216,16 +1250,16 @@
           <t>3세부</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="15" t="n">
         <v>2750000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="15" t="n">
         <v>295806</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="15" t="n">
         <v>3045806</v>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1240,12 +1274,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" style="17" min="1" max="1"/>
+    <col width="14" customWidth="1" style="17" min="2" max="3"/>
+    <col width="26" customWidth="1" style="17" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1276,7 +1309,7 @@
           <t>국제공동워크숍(KIMM 개최)</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="21" t="n">
         <v>46239</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1290,13 +1323,13 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="28.5" customHeight="1" s="17">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>수요기업 사업화 설명회</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="21" t="n">
         <v>46260</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1304,7 +1337,7 @@
           <t>성과관리</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>가스터빈 심포지움 2026 (8.26~28)</t>
         </is>
@@ -1316,8 +1349,8 @@
           <t>운영위원회</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>46280</v>
+      <c r="B4" s="22" t="n">
+        <v>46239</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -1336,7 +1369,7 @@
           <t>2차년도 연차실적보고서 제출</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="21" t="n">
         <v>46433</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1362,423 +1395,339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="6" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" style="17" min="1" max="1"/>
+    <col width="42" customWidth="1" style="17" min="2" max="2"/>
+    <col width="22" customWidth="1" style="17" min="3" max="3"/>
+    <col width="6" customWidth="1" style="17" min="4" max="4"/>
+    <col width="6" customWidth="1" style="17" min="5" max="5"/>
+    <col width="6" customWidth="1" style="17" min="6" max="6"/>
+    <col width="6" customWidth="1" style="17" min="7" max="7"/>
+    <col width="6" customWidth="1" style="17" min="8" max="8"/>
+    <col width="6" customWidth="1" style="17" min="9" max="9"/>
+    <col width="6" customWidth="1" style="17" min="10" max="10"/>
+    <col width="6" customWidth="1" style="17" min="11" max="11"/>
+    <col width="6" customWidth="1" style="17" min="12" max="12"/>
+    <col width="6" customWidth="1" style="17" min="13" max="13"/>
+    <col width="6" customWidth="1" style="17" min="14" max="14"/>
+    <col width="6" customWidth="1" style="17" min="15" max="15"/>
+    <col width="6" customWidth="1" style="17" min="16" max="16"/>
+    <col width="6" customWidth="1" style="17" min="17" max="17"/>
+    <col width="6" customWidth="1" style="17" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>⚠ 자동 생성 탭(계획 기준 미리보기) — 직접 편집 금지. 일정은 '업무리스트'에서 수정 후 python sync_excel.py.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>업무명</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>계획기간</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>'26 1월</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>2월</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="24" t="inlineStr">
         <is>
           <t>4월</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="24" t="inlineStr">
         <is>
           <t>5월</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="24" t="inlineStr">
         <is>
           <t>6월</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="24" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="24" t="inlineStr">
         <is>
           <t>8월</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="24" t="inlineStr">
         <is>
           <t>9월</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="24" t="inlineStr">
         <is>
           <t>10월</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="24" t="inlineStr">
         <is>
           <t>11월</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" s="24" t="inlineStr">
         <is>
           <t>12월</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="P2" s="24" t="inlineStr">
         <is>
           <t>'27 1월</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q2" s="24" t="inlineStr">
         <is>
           <t>2월</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="R2" s="24" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>운영·관리</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>2차년도 협약 체결 및 연구추진체계 정비</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>2026-01-01~2026-02-28</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="n"/>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="n"/>
-      <c r="L3" s="12" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-      <c r="P3" s="12" t="n"/>
-      <c r="Q3" s="12" t="n"/>
-      <c r="R3" s="12" t="n"/>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>4세부 과제 연구 기획 및 선정 평가</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-01~2026-07-31</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="n"/>
+      <c r="E3" s="28" t="n"/>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="29" t="n"/>
+      <c r="H3" s="29" t="n"/>
+      <c r="I3" s="29" t="n"/>
+      <c r="J3" s="29" t="n"/>
+      <c r="K3" s="28" t="n"/>
+      <c r="L3" s="28" t="n"/>
+      <c r="M3" s="28" t="n"/>
+      <c r="N3" s="28" t="n"/>
+      <c r="O3" s="28" t="n"/>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n"/>
+      <c r="R3" s="28" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr"/>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>수소 생산 및 무탄소 발전 핵심 부품 설계·단위기술 성능 확보 추진점검</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr"/>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>운영위원회 개최(국외 1회·국내 1회)</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>2026-04-01~2026-11-30</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="n"/>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="28" t="n"/>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="29" t="n"/>
+      <c r="I4" s="29" t="n"/>
+      <c r="J4" s="29" t="n"/>
+      <c r="K4" s="29" t="n"/>
+      <c r="L4" s="29" t="n"/>
+      <c r="M4" s="29" t="n"/>
+      <c r="N4" s="29" t="n"/>
+      <c r="O4" s="28" t="n"/>
+      <c r="P4" s="28" t="n"/>
+      <c r="Q4" s="28" t="n"/>
+      <c r="R4" s="28" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>국제협력</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>국제워크숍 개최</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>2026-07-01~2026-08-05</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="30" t="n"/>
+      <c r="K5" s="30" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n"/>
+      <c r="R5" s="28" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr"/>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>DLR 해외 인력 파견</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>2026-03-01~2026-12-31</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+      <c r="H6" s="30" t="n"/>
+      <c r="I6" s="30" t="n"/>
+      <c r="J6" s="30" t="n"/>
+      <c r="K6" s="30" t="n"/>
+      <c r="L6" s="30" t="n"/>
+      <c r="M6" s="30" t="n"/>
+      <c r="N6" s="30" t="n"/>
+      <c r="O6" s="30" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n"/>
+      <c r="R6" s="28" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>성과관리</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>수요기업 사업화설명회 개최</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>2026-06-01~2026-09-30</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="31" t="n"/>
+      <c r="J7" s="31" t="n"/>
+      <c r="K7" s="31" t="n"/>
+      <c r="L7" s="31" t="n"/>
+      <c r="M7" s="28" t="n"/>
+      <c r="N7" s="28" t="n"/>
+      <c r="O7" s="28" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n"/>
+      <c r="R7" s="28" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr"/>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>성과지표(논문·특허·기술교류) 관리 및 취합</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>2026-01-01~2026-12-31</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="11" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="11" t="n"/>
-      <c r="M4" s="11" t="n"/>
-      <c r="N4" s="11" t="n"/>
-      <c r="O4" s="11" t="n"/>
-      <c r="P4" s="12" t="n"/>
-      <c r="Q4" s="12" t="n"/>
-      <c r="R4" s="12" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr"/>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>세부과제 연계 강화 및 분기별 진도 점검</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-01~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="12" t="n"/>
-      <c r="R5" s="12" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr"/>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>운영위원회 개최(국외 1회·국내 1회)</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>2026-04-01~2026-11-30</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="12" t="n"/>
-      <c r="R6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>국제협력</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>국제협력 공동연구 본격화 및 DLR 협력 일정 조율</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-01~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="13" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="12" t="n"/>
-      <c r="R7" s="12" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>국제워크숍 개최</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-01~2026-10-31</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="12" t="n"/>
-      <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="12" t="n"/>
-      <c r="R8" s="12" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="31" t="n"/>
+      <c r="I8" s="31" t="n"/>
+      <c r="J8" s="31" t="n"/>
+      <c r="K8" s="31" t="n"/>
+      <c r="L8" s="31" t="n"/>
+      <c r="M8" s="31" t="n"/>
+      <c r="N8" s="31" t="n"/>
+      <c r="O8" s="31" t="n"/>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n"/>
+      <c r="R8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr"/>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>DLR 방문 및 해외 참여기관 인력교류 추진</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-01~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="13" t="n"/>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="13" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="12" t="n"/>
-      <c r="R9" s="12" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>성과관리</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>수요기업 사업화설명회 개최</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-01~2026-09-30</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="14" t="n"/>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="12" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr"/>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>성과지표(논문·특허·기술교류) 관리 및 취합</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>2026-01-01~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="14" t="n"/>
-      <c r="I11" s="14" t="n"/>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="14" t="n"/>
-      <c r="N11" s="14" t="n"/>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="12" t="n"/>
-      <c r="R11" s="12" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>평가·보고</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>2차년도 연차실적 평가 및 연차보고서 작성·제출</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>2026-10-01~2026-12-31</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="15" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="12" t="n"/>
-      <c r="R12" s="12" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="32" t="n"/>
+      <c r="N9" s="32" t="n"/>
+      <c r="O9" s="32" t="n"/>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n"/>
+      <c r="R9" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -829,12 +829,8 @@
       <c r="E3" s="21" t="n">
         <v>46356</v>
       </c>
-      <c r="F3" s="21" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G3" s="21" t="n">
-        <v>46356</v>
-      </c>
+      <c r="F3" s="21" t="n"/>
+      <c r="G3" s="21" t="n"/>
       <c r="H3" s="19" t="inlineStr">
         <is>
           <t>8월 5일 실시</t>
@@ -865,12 +861,8 @@
       <c r="E4" s="22" t="n">
         <v>46239</v>
       </c>
-      <c r="F4" s="22" t="n">
-        <v>46204</v>
-      </c>
-      <c r="G4" s="22" t="n">
-        <v>46239</v>
-      </c>
+      <c r="F4" s="22" t="n"/>
+      <c r="G4" s="22" t="n"/>
       <c r="H4" s="19" t="inlineStr">
         <is>
           <t>8월 5일</t>
@@ -901,11 +893,11 @@
       <c r="E5" s="21" t="n">
         <v>46387</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="22" t="n">
         <v>46082</v>
       </c>
-      <c r="G5" s="21" t="n">
-        <v>46387</v>
+      <c r="G5" s="22" t="n">
+        <v>46173</v>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
@@ -937,12 +929,8 @@
       <c r="E6" s="21" t="n">
         <v>46295</v>
       </c>
-      <c r="F6" s="21" t="n">
-        <v>46174</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>46295</v>
-      </c>
+      <c r="F6" s="21" t="n"/>
+      <c r="G6" s="21" t="n"/>
       <c r="H6" s="20" t="inlineStr">
         <is>
           <t>가스터빈 심포지움 2026 (8.26~28)</t>
@@ -973,11 +961,11 @@
       <c r="E7" s="21" t="n">
         <v>46387</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="22" t="n">
         <v>46023</v>
       </c>
-      <c r="G7" s="21" t="n">
-        <v>46387</v>
+      <c r="G7" s="22" t="n">
+        <v>46202</v>
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
@@ -1009,12 +997,8 @@
       <c r="E8" s="21" t="n">
         <v>46387</v>
       </c>
-      <c r="F8" s="21" t="n">
-        <v>46296</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>46387</v>
-      </c>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="3" t="n"/>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -991,15 +991,19 @@
           <t>2차년도 연차실적 평가 및 연차보고서 작성·제출</t>
         </is>
       </c>
-      <c r="D8" s="21" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>46387</v>
+      <c r="D8" s="22" t="n">
+        <v>46327</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>46356</v>
       </c>
       <c r="F8" s="21" t="n"/>
       <c r="G8" s="21" t="n"/>
-      <c r="H8" s="4" t="n"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>11월 초 작성, 11월 말 제출</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="3" t="n"/>
     </row>
@@ -1353,8 +1357,8 @@
           <t>2차년도 연차실적보고서 제출</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n">
-        <v>46433</v>
+      <c r="B5" s="22" t="n">
+        <v>46356</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -1694,7 +1698,7 @@
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>2026-10-01~2026-12-31</t>
+          <t>2026-11-01~2026-11-30</t>
         </is>
       </c>
       <c r="D9" s="28" t="n"/>
@@ -1706,9 +1710,9 @@
       <c r="J9" s="28" t="n"/>
       <c r="K9" s="28" t="n"/>
       <c r="L9" s="28" t="n"/>
-      <c r="M9" s="32" t="n"/>
+      <c r="M9" s="28" t="n"/>
       <c r="N9" s="32" t="n"/>
-      <c r="O9" s="32" t="n"/>
+      <c r="O9" s="28" t="n"/>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n"/>
       <c r="R9" s="28" t="n"/>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -823,10 +823,10 @@
           <t>운영위원회 개최(국외 1회·국내 1회)</t>
         </is>
       </c>
-      <c r="D3" s="21" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E3" s="21" t="n">
+      <c r="D3" s="22" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E3" s="22" t="n">
         <v>46356</v>
       </c>
       <c r="F3" s="21" t="n"/>
@@ -887,14 +887,14 @@
           <t>DLR 해외 인력 파견</t>
         </is>
       </c>
-      <c r="D5" s="21" t="n">
-        <v>46082</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>46387</v>
+      <c r="D5" s="22" t="n">
+        <v>46068</v>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>46265</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>46082</v>
+        <v>46068</v>
       </c>
       <c r="G5" s="22" t="n">
         <v>46173</v>
@@ -923,11 +923,11 @@
           <t>수요기업 사업화설명회 개최</t>
         </is>
       </c>
-      <c r="D6" s="21" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>46295</v>
+      <c r="D6" s="22" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>46262</v>
       </c>
       <c r="F6" s="21" t="n"/>
       <c r="G6" s="21" t="n"/>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>2026-04-01~2026-11-30</t>
+          <t>2026-08-01~2026-11-30</t>
         </is>
       </c>
       <c r="D4" s="28" t="n"/>
       <c r="E4" s="28" t="n"/>
       <c r="F4" s="28" t="n"/>
-      <c r="G4" s="29" t="n"/>
-      <c r="H4" s="29" t="n"/>
-      <c r="I4" s="29" t="n"/>
-      <c r="J4" s="29" t="n"/>
+      <c r="G4" s="28" t="n"/>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="28" t="n"/>
+      <c r="J4" s="28" t="n"/>
       <c r="K4" s="29" t="n"/>
       <c r="L4" s="29" t="n"/>
       <c r="M4" s="29" t="n"/>
@@ -1606,21 +1606,21 @@
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>2026-03-01~2026-12-31</t>
+          <t>2026-02-15~2026-08-31</t>
         </is>
       </c>
       <c r="D6" s="28" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="E6" s="30" t="n"/>
       <c r="F6" s="30" t="n"/>
       <c r="G6" s="30" t="n"/>
       <c r="H6" s="30" t="n"/>
       <c r="I6" s="30" t="n"/>
       <c r="J6" s="30" t="n"/>
       <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
+      <c r="L6" s="28" t="n"/>
+      <c r="M6" s="28" t="n"/>
+      <c r="N6" s="28" t="n"/>
+      <c r="O6" s="28" t="n"/>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n"/>
       <c r="R6" s="28" t="n"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>2026-06-01~2026-09-30</t>
+          <t>2026-08-01~2026-08-28</t>
         </is>
       </c>
       <c r="D7" s="28" t="n"/>
@@ -1646,10 +1646,10 @@
       <c r="F7" s="28" t="n"/>
       <c r="G7" s="28" t="n"/>
       <c r="H7" s="28" t="n"/>
-      <c r="I7" s="31" t="n"/>
-      <c r="J7" s="31" t="n"/>
+      <c r="I7" s="28" t="n"/>
+      <c r="J7" s="28" t="n"/>
       <c r="K7" s="31" t="n"/>
-      <c r="L7" s="31" t="n"/>
+      <c r="L7" s="28" t="n"/>
       <c r="M7" s="28" t="n"/>
       <c r="N7" s="28" t="n"/>
       <c r="O7" s="28" t="n"/>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="D6" s="22" t="n">
-        <v>46235</v>
+        <v>46260</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="F6" s="21" t="n"/>
       <c r="G6" s="21" t="n"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>2026-08-01~2026-08-28</t>
+          <t>2026-08-26~2026-08-26</t>
         </is>
       </c>
       <c r="D7" s="28" t="n"/>

--- a/data/총괄.xlsx
+++ b/data/총괄.xlsx
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -281,6 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -955,21 +956,17 @@
           <t>성과지표(논문·특허·기술교류) 관리 및 취합</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
-        <v>46023</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>46202</v>
-      </c>
+      <c r="D7" s="22" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>8월 말, 11월 점검 실시</t>
+          <t>8월 말·11월 점검(★)</t>
         </is>
       </c>
       <c r="I7" s="2" t="n"/>
@@ -1261,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="34" customWidth="1" style="17" min="1" max="1"/>
@@ -1368,6 +1365,26 @@
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>KETEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>성과지표 11월 점검</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="n">
+        <v>46356</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>성과관리</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>논문·특허·기술교류 점검</t>
         </is>
       </c>
     </row>
@@ -1666,21 +1683,21 @@
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-12-31</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="31" t="n"/>
-      <c r="F8" s="31" t="n"/>
-      <c r="G8" s="31" t="n"/>
-      <c r="H8" s="31" t="n"/>
-      <c r="I8" s="31" t="n"/>
-      <c r="J8" s="31" t="n"/>
+          <t>2026-08-31~2026-08-31</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="28" t="n"/>
+      <c r="J8" s="28" t="n"/>
       <c r="K8" s="31" t="n"/>
-      <c r="L8" s="31" t="n"/>
-      <c r="M8" s="31" t="n"/>
-      <c r="N8" s="31" t="n"/>
-      <c r="O8" s="31" t="n"/>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="28" t="n"/>
+      <c r="O8" s="28" t="n"/>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n"/>
       <c r="R8" s="28" t="n"/>
